--- a/Dynamics BC Excel Reports/ReportLayouts/Excel/FixedAsset/FixedAssetDetailsExcel.xlsx
+++ b/Dynamics BC Excel Reports/ReportLayouts/Excel/FixedAsset/FixedAssetDetailsExcel.xlsx
@@ -1,83 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr hidePivotFieldList="1"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <x:workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniel.williams\Source\Gold\Yellowstone.Apps\Apps\W1\ExcelReports\app\ReportLayouts\Excel\FixedAsset\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7B1C4D-74CD-458D-BD76-565528203F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="$FixedAssetDetailsPrint$" sheetId="11" r:id="rId1"/>
-    <sheet name="$FixedAssetDetailsAnalysis$" sheetId="13" r:id="rId2"/>
-    <sheet name="$AboutTheReportLabel$" sheetId="12" r:id="rId3"/>
-    <sheet name="NamedMetadata" sheetId="10" state="hidden" r:id="rId4"/>
-    <sheet name="FixedAssetData" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="CaptionData" sheetId="3" state="hidden" r:id="rId6"/>
-    <sheet name="TranslationData" sheetId="2" state="hidden" r:id="rId7"/>
-    <sheet name="Aggregated Metadata" sheetId="4" state="hidden" r:id="rId8"/>
-  </sheets>
-  <definedNames>
-    <definedName name="__">'$AboutTheReportLabel$'!$B$7</definedName>
-    <definedName name="CompanyName">NamedMetadata!$A$1</definedName>
-    <definedName name="DataRetrieved">NamedMetadata!$A$3</definedName>
-    <definedName name="Date">NamedMetadata!$A$2</definedName>
-    <definedName name="FAPostingDateFilter">_xlfn.XLOOKUP("FAPostingDateFilter", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" localSheetId="1">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" localSheetId="1">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="Slicer_DepreciationBookCode">#N/A</definedName>
-    <definedName name="Slicer_FixedAssetClassCode">#N/A</definedName>
-    <definedName name="Slicer_FixedAssetLocation">#N/A</definedName>
-    <definedName name="Slicer_FixedAssetSubclassCode">#N/A</definedName>
-    <definedName name="Slicer_GlobalDimension1Code">#N/A</definedName>
-    <definedName name="Slicer_GlobalDimension2Code">#N/A</definedName>
-  </definedNames>
-  <calcPr calcId="191029" forceFullCalc="1"/>
-  <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId9"/>
-    <pivotCache cacheId="5" r:id="rId10"/>
-  </pivotCaches>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+  <x:bookViews>
+    <x:workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="$FixedAssetDetailsPrint$" sheetId="11" r:id="rId1"/>
+    <x:sheet name="$FixedAssetDetailsAnalysis$" sheetId="13" r:id="rId2"/>
+    <x:sheet name="$AboutTheReportLabel$" sheetId="12" r:id="rId3"/>
+    <x:sheet name="NamedMetadata" sheetId="10" state="hidden" r:id="rId4"/>
+    <x:sheet name="FixedAssetData" sheetId="5" state="hidden" r:id="rId5"/>
+    <x:sheet name="CaptionData" sheetId="3" state="hidden" r:id="rId6"/>
+    <x:sheet name="TranslationData" sheetId="2" state="hidden" r:id="rId7"/>
+    <x:sheet name="Aggregated Metadata" sheetId="4" state="hidden" r:id="rId8"/>
+  </x:sheets>
+  <x:definedNames>
+    <x:definedName name="__">'$AboutTheReportLabel$'!$B$7</x:definedName>
+    <x:definedName name="CompanyName">NamedMetadata!$A$1</x:definedName>
+    <x:definedName name="DataRetrieved">NamedMetadata!$A$3</x:definedName>
+    <x:definedName name="Date">NamedMetadata!$A$2</x:definedName>
+    <x:definedName name="FAPostingDateFilter">_xlfn.XLOOKUP("FAPostingDateFilter", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" localSheetId="1">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" localSheetId="1">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="Slicer_DepreciationBookCode">#N/A</x:definedName>
+    <x:definedName name="Slicer_FixedAssetClassCode">#N/A</x:definedName>
+    <x:definedName name="Slicer_FixedAssetLocation">#N/A</x:definedName>
+    <x:definedName name="Slicer_FixedAssetSubclassCode">#N/A</x:definedName>
+    <x:definedName name="Slicer_GlobalDimension1Code">#N/A</x:definedName>
+    <x:definedName name="Slicer_GlobalDimension2Code">#N/A</x:definedName>
+  </x:definedNames>
+  <x:calcPr calcId="191029" forceFullCalc="1"/>
+  <x:pivotCaches>
+    <x:pivotCache cacheId="3" r:id="rId9"/>
+    <x:pivotCache cacheId="5" r:id="rId10"/>
+  </x:pivotCaches>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
         <x14:slicerCache r:id="rId11"/>
         <x14:slicerCache r:id="rId12"/>
@@ -86,11 +86,11 @@
         <x14:slicerCache r:id="rId15"/>
         <x14:slicerCache r:id="rId16"/>
       </x14:slicerCaches>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+    </x:ext>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    </x:ext>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -100,9 +100,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5473,34 +5473,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{799F1603-B2D3-4CA0-A729-813E36ED0444}" name="FixedAssetData" displayName="FixedAssetData" ref="A1:T2" insertRow="1" totalsRowShown="0" headerRowDxfId="179" dataDxfId="178">
-  <autoFilter ref="A1:T2" xr:uid="{799F1603-B2D3-4CA0-A729-813E36ED0444}"/>
-  <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{0B5D8775-AFC5-4CB4-BFFD-5705D8B74251}" name="DocumentType" dataDxfId="177"/>
-    <tableColumn id="2" xr3:uid="{3EFBA2A8-1194-4C7B-B85D-8224501A9BD9}" name="DocumentNumber" dataDxfId="176"/>
-    <tableColumn id="3" xr3:uid="{F8C1CA9F-99DB-43DA-9EB6-BDA8C3910254}" name="Description" dataDxfId="175"/>
-    <tableColumn id="4" xr3:uid="{020500F7-A2D2-482B-A2F8-F9F81F0C2391}" name="Amount" dataDxfId="174"/>
-    <tableColumn id="5" xr3:uid="{4B5DCCC0-B145-4B52-B29B-0BB5E66DFBC1}" name="EntryNumber" dataDxfId="173"/>
-    <tableColumn id="6" xr3:uid="{38243AD5-C95A-46ED-83F9-025697ED164A}" name="FixedAssetPostingType" dataDxfId="172"/>
-    <tableColumn id="7" xr3:uid="{95E7413F-BC67-4FC8-B869-F3BCA7AE63C7}" name="DepreciationDays" dataDxfId="171"/>
-    <tableColumn id="8" xr3:uid="{04C09D46-A4EE-4836-AC09-E16A36E99C36}" name="UserID" dataDxfId="170"/>
-    <tableColumn id="9" xr3:uid="{899FE06F-5024-4369-80C6-0806E4AD7E2C}" name="PostingDate" dataDxfId="169"/>
-    <tableColumn id="10" xr3:uid="{5077A6E9-5F4F-487B-8B7F-BE4A6E7BD51D}" name="GLEntryNumber" dataDxfId="168"/>
-    <tableColumn id="11" xr3:uid="{F280C469-1AB0-433B-92C4-DD834BE84D80}" name="FixedAssetPostingCategory" dataDxfId="167"/>
-    <tableColumn id="12" xr3:uid="{0221E6DA-5D0E-4468-9FF2-1DFB62596AA6}" name="DepreciationBookCode" dataDxfId="166"/>
-    <tableColumn id="13" xr3:uid="{60263835-0923-44EB-818E-0A74B1A5BB4D}" name="AssetNumber" dataDxfId="165"/>
-    <tableColumn id="14" xr3:uid="{80CC4DDC-6139-494D-8E14-3FCA10088F69}" name="AssetDescription" dataDxfId="164"/>
-    <tableColumn id="15" xr3:uid="{91A8CFEA-FBEA-46DA-94D2-F13BF405A122}" name="FixedAssetClassCode" dataDxfId="163"/>
-    <tableColumn id="16" xr3:uid="{8184EDC5-BE99-4A59-9C1F-883107CF153D}" name="FixedAssetSubclassCode" dataDxfId="162"/>
-    <tableColumn id="18" xr3:uid="{30393DDE-BEE5-45E9-A8E0-DB763445D62E}" name="FixedAssetLocation" dataDxfId="161"/>
-    <tableColumn id="17" xr3:uid="{DACA4B7C-B95F-4E80-8535-EF834F8D21CE}" name="BudgetedAsset" dataDxfId="160">
-      <calculatedColumnFormula>FALSE()</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="19" xr3:uid="{BF350E1E-2F84-4EE9-8AFA-CF723F719D6D}" name="GlobalDimension1Code" dataDxfId="159"/>
-    <tableColumn id="20" xr3:uid="{2E52B5D0-3E76-4635-A43D-0BD15FAA09A3}" name="GlobalDimension2Code" dataDxfId="158"/>
-  </tableColumns>
-  <tableStyleInfo name="Business Central Reports Table Style (Template)" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="FixedAssetData" displayName="FixedAssetData" ref="A1:T2" insertRow="1" totalsRowShown="0" headerRowDxfId="179" dataDxfId="178" xr:uid="{799F1603-B2D3-4CA0-A729-813E36ED0444}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:T2" xr:uid="{799F1603-B2D3-4CA0-A729-813E36ED0444}"/>
+  <x:tableColumns count="20">
+    <x:tableColumn id="1" name="DocumentType" dataDxfId="177" xr3:uid="{0B5D8775-AFC5-4CB4-BFFD-5705D8B74251}"/>
+    <x:tableColumn id="2" name="DocumentNumber" dataDxfId="176" xr3:uid="{3EFBA2A8-1194-4C7B-B85D-8224501A9BD9}"/>
+    <x:tableColumn id="3" name="Description" dataDxfId="175" xr3:uid="{F8C1CA9F-99DB-43DA-9EB6-BDA8C3910254}"/>
+    <x:tableColumn id="4" name="Amount" dataDxfId="174" xr3:uid="{020500F7-A2D2-482B-A2F8-F9F81F0C2391}"/>
+    <x:tableColumn id="5" name="EntryNumber" dataDxfId="173" xr3:uid="{4B5DCCC0-B145-4B52-B29B-0BB5E66DFBC1}"/>
+    <x:tableColumn id="6" name="FixedAssetPostingType" dataDxfId="172" xr3:uid="{38243AD5-C95A-46ED-83F9-025697ED164A}"/>
+    <x:tableColumn id="7" name="DepreciationDays" dataDxfId="171" xr3:uid="{95E7413F-BC67-4FC8-B869-F3BCA7AE63C7}"/>
+    <x:tableColumn id="8" name="UserID" dataDxfId="170" xr3:uid="{04C09D46-A4EE-4836-AC09-E16A36E99C36}"/>
+    <x:tableColumn id="9" name="PostingDate" dataDxfId="169" xr3:uid="{899FE06F-5024-4369-80C6-0806E4AD7E2C}"/>
+    <x:tableColumn id="10" name="GLEntryNumber" dataDxfId="168" xr3:uid="{5077A6E9-5F4F-487B-8B7F-BE4A6E7BD51D}"/>
+    <x:tableColumn id="11" name="FixedAssetPostingCategory" dataDxfId="167" xr3:uid="{F280C469-1AB0-433B-92C4-DD834BE84D80}"/>
+    <x:tableColumn id="12" name="DepreciationBookCode" dataDxfId="166" xr3:uid="{0221E6DA-5D0E-4468-9FF2-1DFB62596AA6}"/>
+    <x:tableColumn id="13" name="AssetNumber" dataDxfId="165" xr3:uid="{60263835-0923-44EB-818E-0A74B1A5BB4D}"/>
+    <x:tableColumn id="14" name="AssetDescription" dataDxfId="164" xr3:uid="{80CC4DDC-6139-494D-8E14-3FCA10088F69}"/>
+    <x:tableColumn id="15" name="FixedAssetClassCode" dataDxfId="163" xr3:uid="{91A8CFEA-FBEA-46DA-94D2-F13BF405A122}"/>
+    <x:tableColumn id="16" name="FixedAssetSubclassCode" dataDxfId="162" xr3:uid="{8184EDC5-BE99-4A59-9C1F-883107CF153D}"/>
+    <x:tableColumn id="18" name="FixedAssetLocation" dataDxfId="161" xr3:uid="{30393DDE-BEE5-45E9-A8E0-DB763445D62E}"/>
+    <x:tableColumn id="17" name="BudgetedAsset" dataDxfId="160" xr3:uid="{DACA4B7C-B95F-4E80-8535-EF834F8D21CE}">
+      <x:calculatedColumnFormula>FALSE()</x:calculatedColumnFormula>
+    </x:tableColumn>
+    <x:tableColumn id="19" name="GlobalDimension1Code" dataDxfId="159" xr3:uid="{BF350E1E-2F84-4EE9-8AFA-CF723F719D6D}"/>
+    <x:tableColumn id="20" name="GlobalDimension2Code" dataDxfId="158" xr3:uid="{2E52B5D0-3E76-4635-A43D-0BD15FAA09A3}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="Business Central Reports Table Style (Template)" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
